--- a/data/payment-08-2026.xlsx
+++ b/data/payment-08-2026.xlsx
@@ -203,7 +203,7 @@
     <col min="1" max="1" width="35.1" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="31.05" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="16.200000000000003" customWidth="1"/>
     <col min="5" max="5" width="41.85" customWidth="1"/>
     <col min="6" max="6" width="41.85" customWidth="1"/>
     <col min="7" max="7" width="12.15" customWidth="1"/>
@@ -369,7 +369,7 @@
     <row r="4">
       <c t="inlineStr" r="A4">
         <is>
-          <t xml:space="preserve">ไทยช่วยไทย พลัส (หน้าร้าน)</t>
+          <t xml:space="preserve">ยิ่งใช้ยิ่งได้</t>
         </is>
       </c>
       <c t="inlineStr" r="B4">
@@ -377,20 +377,20 @@
           <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
-      <c r="D4" s="63">
-        <v>312537</v>
-      </c>
-      <c r="E4" s="63">
-        <v>1360</v>
-      </c>
-      <c r="F4" s="63">
-        <v>311177</v>
+      <c r="D4" s="65">
+        <v>50</v>
+      </c>
+      <c r="E4" s="65">
+        <v>0</v>
+      </c>
+      <c r="F4" s="65">
+        <v>50</v>
       </c>
       <c r="G4" s="65">
         <v>0</v>
       </c>
       <c r="H4" s="66">
-        <v>311177.00</v>
+        <v>50.00</v>
       </c>
       <c r="I4" s="65">
         <v>0</v>
@@ -404,14 +404,14 @@
       <c r="L4" s="65">
         <v>0</v>
       </c>
-      <c r="N4" s="63">
-        <v>311177</v>
+      <c r="N4" s="65">
+        <v>50</v>
       </c>
       <c r="O4" s="65">
         <v>0</v>
       </c>
       <c r="P4" s="65">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q4">
         <is>
@@ -422,7 +422,7 @@
     <row r="5">
       <c t="inlineStr" r="A5">
         <is>
-          <t xml:space="preserve">Cash</t>
+          <t xml:space="preserve">โอนเงิน</t>
         </is>
       </c>
       <c t="inlineStr" r="B5">
@@ -431,19 +431,19 @@
         </is>
       </c>
       <c r="D5" s="63">
-        <v>123432</v>
-      </c>
-      <c r="E5" s="63">
-        <v>1630</v>
+        <v>5500</v>
+      </c>
+      <c r="E5" s="65">
+        <v>0</v>
       </c>
       <c r="F5" s="63">
-        <v>121802</v>
+        <v>5500</v>
       </c>
       <c r="G5" s="65">
         <v>0</v>
       </c>
       <c r="H5" s="66">
-        <v>121802.00</v>
+        <v>5500.00</v>
       </c>
       <c r="I5" s="65">
         <v>0</v>
@@ -457,17 +457,14 @@
       <c r="L5" s="65">
         <v>0</v>
       </c>
-      <c r="M5" s="65">
-        <v>0</v>
-      </c>
       <c r="N5" s="63">
-        <v>121802</v>
+        <v>5500</v>
       </c>
       <c r="O5" s="65">
         <v>0</v>
       </c>
       <c r="P5" s="65">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q5">
         <is>
@@ -478,7 +475,7 @@
     <row r="6">
       <c t="inlineStr" r="A6">
         <is>
-          <t xml:space="preserve">GRAB</t>
+          <t xml:space="preserve">ไทยช่วยไทย พลัส (หน้าร้าน)</t>
         </is>
       </c>
       <c t="inlineStr" r="B6">
@@ -487,19 +484,19 @@
         </is>
       </c>
       <c r="D6" s="63">
-        <v>129484</v>
-      </c>
-      <c r="E6" s="66">
-        <v>103.80</v>
-      </c>
-      <c r="F6" s="64">
-        <v>129380.20</v>
+        <v>519244</v>
+      </c>
+      <c r="E6" s="63">
+        <v>1810</v>
+      </c>
+      <c r="F6" s="63">
+        <v>517434</v>
       </c>
       <c r="G6" s="65">
         <v>0</v>
       </c>
       <c r="H6" s="66">
-        <v>129380.20</v>
+        <v>517434.00</v>
       </c>
       <c r="I6" s="65">
         <v>0</v>
@@ -516,46 +513,46 @@
       <c r="M6" s="65">
         <v>0</v>
       </c>
-      <c r="N6" s="64">
-        <v>129380.20</v>
+      <c r="N6" s="63">
+        <v>517434</v>
       </c>
       <c r="O6" s="65">
         <v>0</v>
       </c>
       <c r="P6" s="65">
-        <v>573</v>
+        <v>220</v>
       </c>
       <c t="inlineStr" r="Q6">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">K Plus</t>
+          <t xml:space="preserve">Cash</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
         <is>
-          <t xml:space="preserve">Dynamic QR</t>
+          <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
       <c r="D7" s="63">
-        <v>114302</v>
-      </c>
-      <c r="E7" s="65">
-        <v>560</v>
+        <v>225185</v>
+      </c>
+      <c r="E7" s="63">
+        <v>2450</v>
       </c>
       <c r="F7" s="63">
-        <v>113742</v>
+        <v>222735</v>
       </c>
       <c r="G7" s="65">
         <v>0</v>
       </c>
       <c r="H7" s="66">
-        <v>113742.00</v>
+        <v>222735.00</v>
       </c>
       <c r="I7" s="65">
         <v>0</v>
@@ -569,14 +566,17 @@
       <c r="L7" s="65">
         <v>0</v>
       </c>
+      <c r="M7" s="65">
+        <v>0</v>
+      </c>
       <c r="N7" s="63">
-        <v>113742</v>
+        <v>222735</v>
       </c>
       <c r="O7" s="65">
         <v>0</v>
       </c>
       <c r="P7" s="65">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c t="inlineStr" r="Q7">
         <is>
@@ -587,7 +587,7 @@
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">LINEMAN</t>
+          <t xml:space="preserve">GRAB</t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
@@ -596,19 +596,19 @@
         </is>
       </c>
       <c r="D8" s="63">
-        <v>39800</v>
-      </c>
-      <c r="E8" s="64">
-        <v>1524.50</v>
+        <v>213340</v>
+      </c>
+      <c r="E8" s="66">
+        <v>103.80</v>
       </c>
       <c r="F8" s="64">
-        <v>38275.50</v>
+        <v>213236.20</v>
       </c>
       <c r="G8" s="65">
         <v>0</v>
       </c>
       <c r="H8" s="66">
-        <v>38275.50</v>
+        <v>213236.20</v>
       </c>
       <c r="I8" s="65">
         <v>0</v>
@@ -626,13 +626,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="64">
-        <v>38275.50</v>
+        <v>213236.20</v>
       </c>
       <c r="O8" s="65">
         <v>0</v>
       </c>
       <c r="P8" s="65">
-        <v>322</v>
+        <v>739</v>
       </c>
       <c t="inlineStr" r="Q8">
         <is>
@@ -643,28 +643,28 @@
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">SHOPEE</t>
+          <t xml:space="preserve">K Plus</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">บันทึกเอง</t>
+          <t xml:space="preserve">Dynamic QR</t>
         </is>
       </c>
       <c r="D9" s="63">
-        <v>15785</v>
-      </c>
-      <c r="E9" s="66">
-        <v>62.90</v>
-      </c>
-      <c r="F9" s="64">
-        <v>15722.10</v>
+        <v>219435</v>
+      </c>
+      <c r="E9" s="63">
+        <v>1070</v>
+      </c>
+      <c r="F9" s="63">
+        <v>218365</v>
       </c>
       <c r="G9" s="65">
         <v>0</v>
       </c>
       <c r="H9" s="66">
-        <v>15722.10</v>
+        <v>218365.00</v>
       </c>
       <c r="I9" s="65">
         <v>0</v>
@@ -678,125 +678,234 @@
       <c r="L9" s="65">
         <v>0</v>
       </c>
-      <c r="M9" s="65">
-        <v>0</v>
-      </c>
-      <c r="N9" s="64">
-        <v>15722.10</v>
+      <c r="N9" s="63">
+        <v>218365</v>
       </c>
       <c r="O9" s="65">
         <v>0</v>
       </c>
       <c r="P9" s="65">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q9">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
+          <t xml:space="preserve">LINEMAN</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B10">
+        <is>
+          <t xml:space="preserve">บันทึกเอง</t>
+        </is>
+      </c>
+      <c r="D10" s="63">
+        <v>77237</v>
+      </c>
+      <c r="E10" s="64">
+        <v>2634.50</v>
+      </c>
+      <c r="F10" s="64">
+        <v>74602.50</v>
+      </c>
+      <c r="G10" s="65">
+        <v>0</v>
+      </c>
+      <c r="H10" s="66">
+        <v>74602.50</v>
+      </c>
+      <c r="I10" s="65">
+        <v>0</v>
+      </c>
+      <c r="J10" s="65">
+        <v>0</v>
+      </c>
+      <c r="K10" s="65">
+        <v>0</v>
+      </c>
+      <c r="L10" s="65">
+        <v>0</v>
+      </c>
+      <c r="M10" s="65">
+        <v>0</v>
+      </c>
+      <c r="N10" s="64">
+        <v>74602.50</v>
+      </c>
+      <c r="O10" s="65">
+        <v>0</v>
+      </c>
+      <c r="P10" s="65">
+        <v>322</v>
+      </c>
+      <c t="inlineStr" r="Q10">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c t="inlineStr" r="A11">
+        <is>
+          <t xml:space="preserve">SHOPEE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B11">
+        <is>
+          <t xml:space="preserve">บันทึกเอง</t>
+        </is>
+      </c>
+      <c r="D11" s="63">
+        <v>25944</v>
+      </c>
+      <c r="E11" s="66">
+        <v>62.90</v>
+      </c>
+      <c r="F11" s="64">
+        <v>25881.10</v>
+      </c>
+      <c r="G11" s="65">
+        <v>0</v>
+      </c>
+      <c r="H11" s="66">
+        <v>25881.10</v>
+      </c>
+      <c r="I11" s="65">
+        <v>0</v>
+      </c>
+      <c r="J11" s="65">
+        <v>0</v>
+      </c>
+      <c r="K11" s="65">
+        <v>0</v>
+      </c>
+      <c r="L11" s="65">
+        <v>0</v>
+      </c>
+      <c r="M11" s="65">
+        <v>0</v>
+      </c>
+      <c r="N11" s="64">
+        <v>25881.10</v>
+      </c>
+      <c r="O11" s="65">
+        <v>0</v>
+      </c>
+      <c r="P11" s="65">
+        <v>165</v>
+      </c>
+      <c t="inlineStr" r="Q11">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c t="inlineStr" r="A12">
+        <is>
           <t xml:space="preserve">Split Amount</t>
         </is>
       </c>
-      <c t="inlineStr" r="B10">
+      <c t="inlineStr" r="B12">
         <is>
           <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
-      <c r="D10" s="63">
-        <v>5255</v>
-      </c>
-      <c r="E10" s="65">
-        <v>0</v>
-      </c>
-      <c r="F10" s="63">
-        <v>5255</v>
-      </c>
-      <c r="G10" s="65">
-        <v>0</v>
-      </c>
-      <c r="H10" s="66">
-        <v>5255.00</v>
-      </c>
-      <c r="I10" s="65">
-        <v>0</v>
-      </c>
-      <c r="J10" s="65">
-        <v>0</v>
-      </c>
-      <c r="K10" s="65">
-        <v>0</v>
-      </c>
-      <c r="L10" s="65">
-        <v>0</v>
-      </c>
-      <c r="N10" s="63">
-        <v>5255</v>
-      </c>
-      <c r="O10" s="65">
-        <v>0</v>
-      </c>
-      <c r="P10" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="Q10">
+      <c r="D12" s="63">
+        <v>9668</v>
+      </c>
+      <c r="E12" s="65">
+        <v>0</v>
+      </c>
+      <c r="F12" s="63">
+        <v>9668</v>
+      </c>
+      <c r="G12" s="65">
+        <v>0</v>
+      </c>
+      <c r="H12" s="66">
+        <v>9668.00</v>
+      </c>
+      <c r="I12" s="65">
+        <v>0</v>
+      </c>
+      <c r="J12" s="65">
+        <v>0</v>
+      </c>
+      <c r="K12" s="65">
+        <v>0</v>
+      </c>
+      <c r="L12" s="65">
+        <v>0</v>
+      </c>
+      <c r="N12" s="63">
+        <v>9668</v>
+      </c>
+      <c r="O12" s="65">
+        <v>0</v>
+      </c>
+      <c r="P12" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="Q12">
         <is>
           <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c t="inlineStr" r="A11" s="2">
+    <row r="13">
+      <c t="inlineStr" r="A13" s="2">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="D11" s="2">
-        <v>740595.00</v>
-      </c>
-      <c r="E11" s="2">
-        <v>5241.20</v>
-      </c>
-      <c r="F11" s="2">
-        <v>735353.80</v>
-      </c>
-      <c r="G11" s="2">
+      <c r="D13" s="2">
+        <v>1295603.00</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8131.20</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1287471.80</v>
+      </c>
+      <c r="G13" s="2">
         <v>0.00</v>
       </c>
-      <c r="H11" s="2">
-        <v>735353.80</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="H13" s="2">
+        <v>1287471.80</v>
+      </c>
+      <c r="I13" s="2">
         <v>0.00</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J13" s="2">
         <v>0.00</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K13" s="2">
         <v>0.00</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L13" s="2">
         <v>0.00</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M13" s="2">
         <v>0.00</v>
       </c>
-      <c r="N11" s="2">
-        <v>735353.80</v>
-      </c>
-      <c r="O11" s="2">
+      <c r="N13" s="2">
+        <v>1287471.80</v>
+      </c>
+      <c r="O13" s="2">
         <v>0.00</v>
       </c>
-      <c r="P11" s="2">
-        <v>1255.00</v>
+      <c r="P13" s="2">
+        <v>1541.00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q10"/>
+  <autoFilter ref="A2:Q12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>

--- a/data/payment-08-2026.xlsx
+++ b/data/payment-08-2026.xlsx
@@ -483,20 +483,20 @@
           <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
-      <c r="D6" s="63">
-        <v>519244</v>
-      </c>
-      <c r="E6" s="63">
-        <v>1810</v>
-      </c>
-      <c r="F6" s="63">
-        <v>517434</v>
+      <c r="D6" s="65">
+        <v>660</v>
+      </c>
+      <c r="E6" s="65">
+        <v>0</v>
+      </c>
+      <c r="F6" s="65">
+        <v>660</v>
       </c>
       <c r="G6" s="65">
         <v>0</v>
       </c>
       <c r="H6" s="66">
-        <v>517434.00</v>
+        <v>660.00</v>
       </c>
       <c r="I6" s="65">
         <v>0</v>
@@ -510,28 +510,25 @@
       <c r="L6" s="65">
         <v>0</v>
       </c>
-      <c r="M6" s="65">
-        <v>0</v>
-      </c>
-      <c r="N6" s="63">
-        <v>517434</v>
+      <c r="N6" s="65">
+        <v>660</v>
       </c>
       <c r="O6" s="65">
         <v>0</v>
       </c>
       <c r="P6" s="65">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q6">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c t="inlineStr" r="A7">
         <is>
-          <t xml:space="preserve">Cash</t>
+          <t xml:space="preserve">ไทยช่วยไทย พลัส (หน้าร้าน)</t>
         </is>
       </c>
       <c t="inlineStr" r="B7">
@@ -540,19 +537,19 @@
         </is>
       </c>
       <c r="D7" s="63">
-        <v>225185</v>
+        <v>606067</v>
       </c>
       <c r="E7" s="63">
-        <v>2450</v>
+        <v>1820</v>
       </c>
       <c r="F7" s="63">
-        <v>222735</v>
+        <v>604247</v>
       </c>
       <c r="G7" s="65">
         <v>0</v>
       </c>
       <c r="H7" s="66">
-        <v>222735.00</v>
+        <v>604247.00</v>
       </c>
       <c r="I7" s="65">
         <v>0</v>
@@ -570,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="63">
-        <v>222735</v>
+        <v>604247</v>
       </c>
       <c r="O7" s="65">
         <v>0</v>
       </c>
       <c r="P7" s="65">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c t="inlineStr" r="Q7">
         <is>
@@ -587,7 +584,7 @@
     <row r="8">
       <c t="inlineStr" r="A8">
         <is>
-          <t xml:space="preserve">GRAB</t>
+          <t xml:space="preserve">Cash</t>
         </is>
       </c>
       <c t="inlineStr" r="B8">
@@ -596,19 +593,19 @@
         </is>
       </c>
       <c r="D8" s="63">
-        <v>213340</v>
-      </c>
-      <c r="E8" s="66">
-        <v>103.80</v>
-      </c>
-      <c r="F8" s="64">
-        <v>213236.20</v>
+        <v>280234</v>
+      </c>
+      <c r="E8" s="63">
+        <v>2900</v>
+      </c>
+      <c r="F8" s="63">
+        <v>277334</v>
       </c>
       <c r="G8" s="65">
         <v>0</v>
       </c>
       <c r="H8" s="66">
-        <v>213236.20</v>
+        <v>277334.00</v>
       </c>
       <c r="I8" s="65">
         <v>0</v>
@@ -625,46 +622,46 @@
       <c r="M8" s="65">
         <v>0</v>
       </c>
-      <c r="N8" s="64">
-        <v>213236.20</v>
+      <c r="N8" s="63">
+        <v>277334</v>
       </c>
       <c r="O8" s="65">
         <v>0</v>
       </c>
       <c r="P8" s="65">
-        <v>739</v>
+        <v>95</v>
       </c>
       <c t="inlineStr" r="Q8">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c t="inlineStr" r="A9">
         <is>
-          <t xml:space="preserve">K Plus</t>
+          <t xml:space="preserve">GRAB</t>
         </is>
       </c>
       <c t="inlineStr" r="B9">
         <is>
-          <t xml:space="preserve">Dynamic QR</t>
+          <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
       <c r="D9" s="63">
-        <v>219435</v>
-      </c>
-      <c r="E9" s="63">
-        <v>1070</v>
-      </c>
-      <c r="F9" s="63">
-        <v>218365</v>
+        <v>252350</v>
+      </c>
+      <c r="E9" s="66">
+        <v>193.80</v>
+      </c>
+      <c r="F9" s="64">
+        <v>252156.20</v>
       </c>
       <c r="G9" s="65">
         <v>0</v>
       </c>
       <c r="H9" s="66">
-        <v>218365.00</v>
+        <v>252156.20</v>
       </c>
       <c r="I9" s="65">
         <v>0</v>
@@ -678,46 +675,49 @@
       <c r="L9" s="65">
         <v>0</v>
       </c>
-      <c r="N9" s="63">
-        <v>218365</v>
+      <c r="M9" s="65">
+        <v>0</v>
+      </c>
+      <c r="N9" s="64">
+        <v>252156.20</v>
       </c>
       <c r="O9" s="65">
         <v>0</v>
       </c>
-      <c r="P9" s="65">
-        <v>0</v>
+      <c r="P9" s="63">
+        <v>1252</v>
       </c>
       <c t="inlineStr" r="Q9">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c t="inlineStr" r="A10">
         <is>
-          <t xml:space="preserve">LINEMAN</t>
+          <t xml:space="preserve">K Plus</t>
         </is>
       </c>
       <c t="inlineStr" r="B10">
         <is>
-          <t xml:space="preserve">บันทึกเอง</t>
+          <t xml:space="preserve">Dynamic QR</t>
         </is>
       </c>
       <c r="D10" s="63">
-        <v>77237</v>
-      </c>
-      <c r="E10" s="64">
-        <v>2634.50</v>
-      </c>
-      <c r="F10" s="64">
-        <v>74602.50</v>
+        <v>289929</v>
+      </c>
+      <c r="E10" s="63">
+        <v>1310</v>
+      </c>
+      <c r="F10" s="63">
+        <v>288619</v>
       </c>
       <c r="G10" s="65">
         <v>0</v>
       </c>
       <c r="H10" s="66">
-        <v>74602.50</v>
+        <v>288619.00</v>
       </c>
       <c r="I10" s="65">
         <v>0</v>
@@ -731,28 +731,25 @@
       <c r="L10" s="65">
         <v>0</v>
       </c>
-      <c r="M10" s="65">
-        <v>0</v>
-      </c>
-      <c r="N10" s="64">
-        <v>74602.50</v>
+      <c r="N10" s="63">
+        <v>288619</v>
       </c>
       <c r="O10" s="65">
         <v>0</v>
       </c>
       <c r="P10" s="65">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="Q10">
         <is>
-          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c t="inlineStr" r="A11">
         <is>
-          <t xml:space="preserve">SHOPEE</t>
+          <t xml:space="preserve">LINEMAN</t>
         </is>
       </c>
       <c t="inlineStr" r="B11">
@@ -761,19 +758,19 @@
         </is>
       </c>
       <c r="D11" s="63">
-        <v>25944</v>
-      </c>
-      <c r="E11" s="66">
-        <v>62.90</v>
+        <v>97125</v>
+      </c>
+      <c r="E11" s="64">
+        <v>3136.75</v>
       </c>
       <c r="F11" s="64">
-        <v>25881.10</v>
+        <v>93988.25</v>
       </c>
       <c r="G11" s="65">
         <v>0</v>
       </c>
       <c r="H11" s="66">
-        <v>25881.10</v>
+        <v>93988.25</v>
       </c>
       <c r="I11" s="65">
         <v>0</v>
@@ -791,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="64">
-        <v>25881.10</v>
+        <v>93988.25</v>
       </c>
       <c r="O11" s="65">
         <v>0</v>
       </c>
       <c r="P11" s="65">
-        <v>165</v>
+        <v>322</v>
       </c>
       <c t="inlineStr" r="Q11">
         <is>
@@ -808,104 +805,211 @@
     <row r="12">
       <c t="inlineStr" r="A12">
         <is>
+          <t xml:space="preserve">Line Man - Rabbit Linepay</t>
+        </is>
+      </c>
+      <c r="D12" s="63">
+        <v>99358</v>
+      </c>
+      <c r="E12" s="64">
+        <v>3366.75</v>
+      </c>
+      <c r="F12" s="64">
+        <v>95991.25</v>
+      </c>
+      <c r="G12" s="65">
+        <v>0</v>
+      </c>
+      <c r="H12" s="66">
+        <v>95991.25</v>
+      </c>
+      <c r="I12" s="65">
+        <v>0</v>
+      </c>
+      <c r="J12" s="65">
+        <v>0</v>
+      </c>
+      <c r="K12" s="65">
+        <v>0</v>
+      </c>
+      <c r="L12" s="65">
+        <v>0</v>
+      </c>
+      <c r="M12" s="66">
+        <v>0.00</v>
+      </c>
+      <c r="N12" s="64">
+        <v>95991.25</v>
+      </c>
+      <c r="O12" s="65">
+        <v>0</v>
+      </c>
+      <c r="P12" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="Q12">
+        <is>
+          <t xml:space="preserve">ตลาดหน้าศาล</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c t="inlineStr" r="A13">
+        <is>
+          <t xml:space="preserve">SHOPEE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="B13">
+        <is>
+          <t xml:space="preserve">บันทึกเอง</t>
+        </is>
+      </c>
+      <c r="D13" s="63">
+        <v>33496</v>
+      </c>
+      <c r="E13" s="66">
+        <v>62.90</v>
+      </c>
+      <c r="F13" s="64">
+        <v>33433.10</v>
+      </c>
+      <c r="G13" s="65">
+        <v>0</v>
+      </c>
+      <c r="H13" s="66">
+        <v>33433.10</v>
+      </c>
+      <c r="I13" s="65">
+        <v>0</v>
+      </c>
+      <c r="J13" s="65">
+        <v>0</v>
+      </c>
+      <c r="K13" s="65">
+        <v>0</v>
+      </c>
+      <c r="L13" s="65">
+        <v>0</v>
+      </c>
+      <c r="M13" s="65">
+        <v>0</v>
+      </c>
+      <c r="N13" s="64">
+        <v>33433.10</v>
+      </c>
+      <c r="O13" s="65">
+        <v>0</v>
+      </c>
+      <c r="P13" s="65">
+        <v>165</v>
+      </c>
+      <c t="inlineStr" r="Q13">
+        <is>
+          <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - บ้านชูชิ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c t="inlineStr" r="A14">
+        <is>
           <t xml:space="preserve">Split Amount</t>
         </is>
       </c>
-      <c t="inlineStr" r="B12">
+      <c t="inlineStr" r="B14">
         <is>
           <t xml:space="preserve">บันทึกเอง</t>
         </is>
       </c>
-      <c r="D12" s="63">
-        <v>9668</v>
-      </c>
-      <c r="E12" s="65">
-        <v>0</v>
-      </c>
-      <c r="F12" s="63">
-        <v>9668</v>
-      </c>
-      <c r="G12" s="65">
-        <v>0</v>
-      </c>
-      <c r="H12" s="66">
-        <v>9668.00</v>
-      </c>
-      <c r="I12" s="65">
-        <v>0</v>
-      </c>
-      <c r="J12" s="65">
-        <v>0</v>
-      </c>
-      <c r="K12" s="65">
-        <v>0</v>
-      </c>
-      <c r="L12" s="65">
-        <v>0</v>
-      </c>
-      <c r="N12" s="63">
-        <v>9668</v>
-      </c>
-      <c r="O12" s="65">
-        <v>0</v>
-      </c>
-      <c r="P12" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="Q12">
+      <c r="D14" s="63">
+        <v>12260</v>
+      </c>
+      <c r="E14" s="65">
+        <v>100</v>
+      </c>
+      <c r="F14" s="63">
+        <v>12160</v>
+      </c>
+      <c r="G14" s="65">
+        <v>0</v>
+      </c>
+      <c r="H14" s="66">
+        <v>12160.00</v>
+      </c>
+      <c r="I14" s="65">
+        <v>0</v>
+      </c>
+      <c r="J14" s="65">
+        <v>0</v>
+      </c>
+      <c r="K14" s="65">
+        <v>0</v>
+      </c>
+      <c r="L14" s="65">
+        <v>0</v>
+      </c>
+      <c r="N14" s="63">
+        <v>12160</v>
+      </c>
+      <c r="O14" s="65">
+        <v>0</v>
+      </c>
+      <c r="P14" s="65">
+        <v>0</v>
+      </c>
+      <c t="inlineStr" r="Q14">
         <is>
           <t xml:space="preserve">ซูชิแซลมอนเดย์ Salmon's Day - ตลาดหน้าศาลชลบุรี</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c t="inlineStr" r="A13" s="2">
+    <row r="15">
+      <c t="inlineStr" r="A15" s="2">
         <is>
           <t xml:space="preserve">Total</t>
         </is>
       </c>
-      <c r="D13" s="2">
-        <v>1295603.00</v>
-      </c>
-      <c r="E13" s="2">
-        <v>8131.20</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1287471.80</v>
-      </c>
-      <c r="G13" s="2">
+      <c r="D15" s="2">
+        <v>1677029.00</v>
+      </c>
+      <c r="E15" s="2">
+        <v>12890.20</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1664138.80</v>
+      </c>
+      <c r="G15" s="2">
         <v>0.00</v>
       </c>
-      <c r="H13" s="2">
-        <v>1287471.80</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="H15" s="2">
+        <v>1664138.80</v>
+      </c>
+      <c r="I15" s="2">
         <v>0.00</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J15" s="2">
         <v>0.00</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K15" s="2">
         <v>0.00</v>
       </c>
-      <c r="L13" s="2">
+      <c r="L15" s="2">
         <v>0.00</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M15" s="2">
         <v>0.00</v>
       </c>
-      <c r="N13" s="2">
-        <v>1287471.80</v>
-      </c>
-      <c r="O13" s="2">
+      <c r="N15" s="2">
+        <v>1664138.80</v>
+      </c>
+      <c r="O15" s="2">
         <v>0.00</v>
       </c>
-      <c r="P13" s="2">
-        <v>1541.00</v>
+      <c r="P15" s="2">
+        <v>2054.00</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q12"/>
+  <autoFilter ref="A2:Q14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
